--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1469-573-CM25</t>
+          <t>709603-45-SE25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,48 +717,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>21196.66</v>
+        <v>42876.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>812799-105-CM25</t>
+          <t>1469-573-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -778,48 +782,52 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>20687.61</v>
+        <v>21196.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057414-113-CM25</t>
+          <t>812799-105-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,27 +852,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +882,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>251095.95</v>
+        <v>20687.61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057539-16153-CM25</t>
+          <t>1057414-113-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,48 +908,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>58749.2</v>
+        <v>251095.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1232911-28-CM25</t>
+          <t>1057539-16153-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,37 +968,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.115.629-7</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes de Colina</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LUUK SPA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.363.384-3</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +1008,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>41455.89</v>
+        <v>58749.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>731-48-CM25</t>
+          <t>1232911-28-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1029,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1039,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.008.000-6</t>
+          <t>65.115.629-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MENORES</t>
+          <t>Corporación Municipal de Deportes de Colina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,28 +1054,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>LUUK SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>77.363.384-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>69941.44</v>
+        <v>41455.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3073-202-CM25</t>
+          <t>731-48-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,27 +1104,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>61.008.000-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOCIEDAD LIGARIUS SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.063.547-0</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1134,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10142.62</v>
+        <v>69941.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>881-52-CM25</t>
+          <t>3073-202-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,27 +1165,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>SOCIEDAD LIGARIUS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>77.063.547-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1195,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>38991.88</v>
+        <v>10142.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4205-103-CM25</t>
+          <t>881-52-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,43 +1226,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.073.900-3</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAVI</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NAPSIS SPA.</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.093.358-9</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>16671.02</v>
+        <v>38991.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2422-401-CM25</t>
+          <t>4205-103-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1281,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1291,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.072.100-7</t>
+          <t>69.073.900-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
+          <t>I MUNICIPALIDAD DE CURACAVI</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1306,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Geosolve Cia Ltda</t>
+          <t>NAPSIS SPA.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.562.690-0</t>
+          <t>76.093.358-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,7 +1321,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>20329.89</v>
+        <v>16671.02</v>
       </c>
     </row>
     <row r="15">
@@ -1490,7 +1510,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1393575-45-CM25</t>
+          <t>2422-401-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1525,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1535,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.010.882-5</t>
+          <t>69.072.100-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>FUNDACION IMAGEN DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1550,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Geosolve Cia Ltda</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.562.690-0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1565,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>9987.82</v>
+        <v>20329.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1016414-35-CM25</t>
+          <t>1393575-45-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,12 +1596,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.909.000-6</t>
+          <t>65.010.882-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE TELEVISION</t>
+          <t>FUNDACION IMAGEN DE CHILE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,28 +1611,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CLARO CHILE S.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.799.250-k</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>69873.17</v>
+        <v>9987.82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3894-8-CM25</t>
+          <t>1016414-35-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,17 +1656,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>60.909.000-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,22 +1676,26 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SolNet SPA</t>
+          <t>CLARO CHILE S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>22346.76</v>
+        <v>69873.17</v>
       </c>
     </row>
     <row r="21">
@@ -1734,7 +1762,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>937232-1307-CM24</t>
+          <t>3894-8-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1777,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.980.620-4</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1802,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SOCIEDAD LIGARIUS SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.063.547-0</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1817,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>240631.83</v>
+        <v>22346.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2268-70-CM25</t>
+          <t>937232-1307-CM24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1843,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.608.700-2</t>
+          <t>61.980.620-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
+          <t>CENTRO DE REFERENCIA DE SALUD HOSPITAL PROVINCIA CORDILLERA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1863,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ASIMOV CONSULTORES SPA</t>
+          <t>SOCIEDAD LIGARIUS SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.372.725-4</t>
+          <t>77.063.547-0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1878,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>42994.6</v>
+        <v>240631.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1588-2-CM25</t>
+          <t>2268-70-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1899,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>61.608.700-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>CENTRAL DE ABASTECIMIENTO DEL SISTEMA NACIONAL DE SERVICIO DE SALUD</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1924,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>ASIMOV CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.372.725-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1939,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9482.01</v>
+        <v>42994.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1111089-119-CM25</t>
+          <t>1588-2-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +1965,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,28 +1985,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ABENIS</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.217.169-4</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>244891.94</v>
+        <v>9482.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1725-4628-CM25</t>
+          <t>1111089-119-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,48 +2030,52 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>ABENIS</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.217.169-4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>13976.96</v>
+        <v>244891.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1557-115-CM25</t>
+          <t>1725-4628-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,27 +2100,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2130,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>12735.73</v>
+        <v>13976.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1111089-174-CM25</t>
+          <t>1557-115-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,53 +2151,57 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ABENIS</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.217.169-4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>62542.78</v>
+        <v>12735.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1588-21-CM25</t>
+          <t>1385462-38-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,12 +2226,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>72.443.600-5</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,22 +2241,26 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ACS INGENIEROS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.240.927-5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>19083.99</v>
+        <v>6654.76</v>
       </c>
     </row>
     <row r="30">
@@ -2270,7 +2314,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2283,7 +2331,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1385462-38-CM25</t>
+          <t>1111089-174-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2351,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,28 +2371,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>ABENIS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.217.169-4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6654.76</v>
+        <v>62542.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5403-24-CM25</t>
+          <t>1588-21-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,22 +2411,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>72.443.600-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>SERVICIO DE EVALUACION AMBIENTAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2436,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>ACS INGENIEROS SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
+          <t>76.240.927-5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2451,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>250544.81</v>
+        <v>19083.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5707-131-CM25</t>
+          <t>5403-24-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2472,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2497,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NETICS SPA</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.363.873-1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>77.622.841-9</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>12444.46</v>
+        <v>250544.81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5707-130-CM25</t>
+          <t>1314-65-CM24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2542,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,28 +2562,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NETICS SPA</t>
+          <t>DEL MAR TECHNOLOGY GROUP SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.363.873-1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>76.522.861-1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7812.34</v>
+        <v>32196.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1469-796-CM25</t>
+          <t>876-102-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,32 +2607,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.101.000-3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SECRETARIA GENERAL DE GOBIERNO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>SERVICIOS DE CONSULTORIA VALPOSYSTEMS LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>76.164.712-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2642,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>13304.13</v>
+        <v>60283.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1314-65-CM24</t>
+          <t>5707-130-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,17 +2668,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2688,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DEL MAR TECHNOLOGY GROUP SPA</t>
+          <t>NETICS SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.522.861-1</t>
+          <t>76.363.873-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2703,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>32196.95</v>
+        <v>7812.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>876-102-CM25</t>
+          <t>5707-131-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2674,12 +2734,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.101.000-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SECRETARIA GENERAL DE GOBIERNO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2749,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SERVICIOS DE CONSULTORIA VALPOSYSTEMS LIMITADA</t>
+          <t>NETICS SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.164.712-1</t>
+          <t>76.363.873-1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2764,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>60283.74</v>
+        <v>12444.46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3447-1175-CM25</t>
+          <t>1469-796-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,37 +2785,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2825,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>34488.12</v>
+        <v>13304.13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>711841-182-CM25</t>
+          <t>3447-1175-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,43 +2856,47 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>50063.41</v>
+        <v>34488.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>812261-1268-CM24</t>
+          <t>711841-182-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2911,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2921,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2936,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kibernum S.A</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.616.770-k</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2951,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>138546.34</v>
+        <v>50063.41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>812261-1322-CM24</t>
+          <t>812261-1268-CM24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2948,13 +3012,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>262605.26</v>
+        <v>138546.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1561-68-CM25</t>
+          <t>812261-1322-CM24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,12 +3043,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +3058,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CODER HUB SPA</t>
+          <t>Kibernum S.A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.734.221-7</t>
+          <t>96.616.770-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3073,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>22754.88</v>
+        <v>262605.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5655-23-CM25</t>
+          <t>1561-68-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,12 +3104,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,28 +3119,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>G-Talent SPA</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>52.004.665-8</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>76.734.221-7</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14965.14</v>
+        <v>22754.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4467-2-CM25</t>
+          <t>5655-23-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3159,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3169,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,28 +3184,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CMETRIX  BUSINESS SOLUTIONS S.A</t>
+          <t>G-Talent SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.969.290-2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>52.004.665-8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>61770.81</v>
+        <v>14965.14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1614-36-CM25</t>
+          <t>4467-2-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3224,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3234,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.510.000-7</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3249,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>CMETRIX  BUSINESS SOLUTIONS S.A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>96.969.290-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3264,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7332.39</v>
+        <v>61770.81</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>587-168-CM25</t>
+          <t>1614-36-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3223,12 +3295,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.510.000-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3246,20 +3318,24 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>18729.48</v>
+        <v>7332.39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2793-425-CM25</t>
+          <t>587-168-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,17 +3355,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,28 +3375,32 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>33364.74</v>
+        <v>18729.48</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1191449-38-CM25</t>
+          <t>2793-425-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3340,17 +3420,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.905.006-3</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,28 +3440,32 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BLUE COMPANY S A</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.981.410-2</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8052.16</v>
+        <v>33364.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2083-1-CM25</t>
+          <t>1191449-38-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,12 +3490,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>71.294.800-0</t>
+          <t>60.905.006-3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3505,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ESRI CHILE S A</t>
+          <t>BLUE COMPANY S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.504.980-6</t>
+          <t>96.981.410-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3520,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>45562.46</v>
+        <v>8052.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4130-23-CM25</t>
+          <t>2083-1-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3541,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3551,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.101.020-6</t>
+          <t>71.294.800-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CENTRO DE INFORMACION DE RECURSOS NATURALES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,28 +3566,32 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>USERCODE SPA</t>
+          <t>ESRI CHILE S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.347.464-8</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.504.980-6</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>12433.14</v>
+        <v>45562.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2450-241-CM25</t>
+          <t>4130-23-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,43 +3616,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.101.020-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IMPACTE SPA</t>
+          <t>USERCODE SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.572.009-5</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>77.347.464-8</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11804.32</v>
+        <v>12433.14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3734-305-CM25</t>
+          <t>2450-241-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,53 +3671,57 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>IMPACTE SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>76.572.009-5</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6969.2</v>
+        <v>11804.32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2483-292-CM25</t>
+          <t>3734-305-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3650,43 +3746,47 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>16489.49</v>
+        <v>6969.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>688-67-CM25</t>
+          <t>2483-292-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3706,17 +3806,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3826,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.153.158-1</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3841,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>6969.2</v>
+        <v>16489.49</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>584105-208-CM25</t>
+          <t>688-67-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,12 +3872,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.979.830-9</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ENERGIA</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3887,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Integracion de Tecnologias ITQ Limitada</t>
+          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.092.207-2</t>
+          <t>76.153.158-1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3902,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>57093.33</v>
+        <v>6969.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1607-86-CM25</t>
+          <t>584105-208-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,12 +3933,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3948,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>Integracion de Tecnologias ITQ Limitada</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.092.207-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3963,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>629930.14</v>
+        <v>57093.33</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>538598-3616-CM25</t>
+          <t>1607-86-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,12 +3994,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.979.450-8</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+          <t>SUPERINTENDENCIA DE SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,28 +4009,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>W INGENIEROS</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.300.938-6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>77.430.680-3</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>55370.61</v>
+        <v>629930.14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057539-16834-CM25</t>
+          <t>538598-3616-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3950,32 +4054,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.979.450-8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>W INGENIEROS</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
+          <t>76.300.938-6</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +4089,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>36693.08</v>
+        <v>55370.61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>604944-15-CM25</t>
+          <t>1057539-16834-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,37 +4110,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.979.870-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DEFENSA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>BROWSE INGENIERIA DE SOFTWARE SOCIEDAD ANONIMA</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>79.822.840-4</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4150,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>50256.75</v>
+        <v>36693.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>45-110-CM25</t>
+          <t>604944-15-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4077,12 +4181,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.979.870-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DE DEFENSA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4196,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ACS INGENIEROS SPA</t>
+          <t>BROWSE INGENIERIA DE SOFTWARE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.240.927-5</t>
+          <t>79.822.840-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4211,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>24277.12</v>
+        <v>50256.75</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1233623-144-CM25</t>
+          <t>45-110-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,27 +4242,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>ACS INGENIEROS SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.240.927-5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4272,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>29772.05</v>
+        <v>24277.12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1602-43-CM25</t>
+          <t>1233623-144-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4199,43 +4303,47 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>49873.65</v>
+        <v>29772.05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1048-195-CM25</t>
+          <t>1602-43-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4260,43 +4368,47 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Zecovery Ltda   -    EXEC</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>22149.57</v>
+        <v>49873.65</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2659-231-CM25</t>
+          <t>1048-195-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4423,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,43 +4433,47 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MEETCARD</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.437.288-3</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>27128.29</v>
+        <v>22149.57</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2216-237-CM25</t>
+          <t>2659-231-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,17 +4493,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MOP Dirección General de Concesiones</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4513,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>MEETCARD</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.437.288-3</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4528,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>281394.16</v>
+        <v>27128.29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>875-42-CM25</t>
+          <t>2216-237-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4438,17 +4554,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.720.000-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4574,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>BPM CONSULTING SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.101.697-9</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4589,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>29603.59</v>
+        <v>281394.16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1876-52-CM25</t>
+          <t>875-42-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4504,12 +4620,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>60.720.000-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4635,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
+          <t>BPM CONSULTING SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.093.443-7</t>
+          <t>77.101.697-9</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4650,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>514712.49</v>
+        <v>29603.59</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4127-187-CM25</t>
+          <t>1876-52-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4565,12 +4681,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.975.700-9</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,28 +4696,32 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>SERVICIOS TECNOLOGICOS ADEMANDA.COM LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>76.093.443-7</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>13564.15</v>
+        <v>514712.49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>770-65-CM25</t>
+          <t>4127-187-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4736,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4746,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.604.000-8</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4761,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4776,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>40876.63</v>
+        <v>13564.15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>761-234-CM25</t>
+          <t>770-65-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4687,12 +4807,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.604.000-8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4822,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4837,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>24718.17</v>
+        <v>40876.63</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2109-789-CM25</t>
+          <t>761-234-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4748,12 +4868,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4883,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Georg</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4898,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>33648.12</v>
+        <v>24718.17</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2305-26-CM25</t>
+          <t>1057547-21069-SE25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,43 +4929,47 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>43645.82</v>
+        <v>46743.26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2673-93-CM25</t>
+          <t>2109-789-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,17 +4989,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>61.608.203-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,82 +5009,216 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Georg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>41161.81</v>
+        <v>33648.12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>2305-26-CM25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>61.973.000-3</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>43645.82</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2673-93-CM25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>69.072.900-8</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>41161.81</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>1385462-51-CM25</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>abr-2025</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>61.981.340-5</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
         <is>
           <t>LFI SPA</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>76.044.285-2</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="n">
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
         <v>46241.92</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2025.xlsx
@@ -2635,7 +2635,11 @@
           <t>76.164.712-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3005,7 +3009,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3066,7 +3074,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
